--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130250024</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130250080</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93048</v>
+        <v>93051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130250024</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130250080</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93051</v>
+        <v>93077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93077</v>
+        <v>93078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130250024</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130250080</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93079</v>
+        <v>93081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>130250050</v>
       </c>
       <c r="B4" t="n">
-        <v>93081</v>
+        <v>93085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,6 +1002,115 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130911242</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575307</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6395114</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,558 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131475431</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91817</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575279</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6395392</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ovanligt med ullticka på barklös låga!</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131475540</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575309</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6395395</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosök, gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131475580</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575316</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6395394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök, gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131475653</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575305</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6395392</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131475471</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91817</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575295</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6395398</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92251</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92253</v>
+        <v>92256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>131475431</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131475540</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
         <v>131475580</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
         <v>131475653</v>
       </c>
       <c r="B9" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>131475471</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,6 +1663,453 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133532794</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575276</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6395404</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På barklös granlåga!</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133532677</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575233</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6395408</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133533137</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575303</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6395378</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133532871</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92342</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575311</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6395391</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lite osäker på substrat, men möjligen gran!</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -1889,32 +1889,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133533137</v>
+        <v>133532871</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>92342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1922,13 +1922,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1936,13 +1935,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575303</v>
+        <v>575311</v>
       </c>
       <c r="R13" t="n">
-        <v>6395378</v>
+        <v>6395391</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,12 +1973,18 @@
           <t>2026-05-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lite osäker på substrat, men möjligen gran!</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1998,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133532871</v>
+        <v>133533137</v>
       </c>
       <c r="B14" t="n">
-        <v>92342</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2031,12 +2036,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2044,13 +2050,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575311</v>
+        <v>575303</v>
       </c>
       <c r="R14" t="n">
-        <v>6395391</v>
+        <v>6395378</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,18 +2088,12 @@
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Lite osäker på substrat, men möjligen gran!</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130250024</v>
+        <v>131475431</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575351</v>
+        <v>575279</v>
       </c>
       <c r="R2" t="n">
-        <v>6395351</v>
+        <v>6395392</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Ovanligt med ullticka på barklös låga!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,17 +782,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130250080</v>
+        <v>131475471</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,31 +800,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575236</v>
+        <v>575295</v>
       </c>
       <c r="R3" t="n">
-        <v>6395421</v>
+        <v>6395398</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,17 +891,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130250050</v>
+        <v>133532794</v>
       </c>
       <c r="B4" t="n">
-        <v>93085</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,31 +909,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -941,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575262</v>
+        <v>575276</v>
       </c>
       <c r="R4" t="n">
-        <v>6395315</v>
+        <v>6395404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På barklös granlåga!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,39 +1005,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130911242</v>
+        <v>131475653</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575307</v>
+        <v>575305</v>
       </c>
       <c r="R5" t="n">
-        <v>6395114</v>
+        <v>6395392</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,6 +1102,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1106,39 +1114,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131475431</v>
+        <v>133532871</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>92370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1159,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575279</v>
+        <v>575311</v>
       </c>
       <c r="R6" t="n">
-        <v>6395392</v>
+        <v>6395391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,17 +1197,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ovanligt med ullticka på barklös låga!</t>
+          <t>Lite osäker på substrat, men möjligen gran!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,17 +1228,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131475540</v>
+        <v>130250005</v>
       </c>
       <c r="B7" t="n">
-        <v>57911</v>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,42 +1246,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 61552, Försjönäs, Sm</t>
+          <t>Försjönäs, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575309</v>
+        <v>575585</v>
       </c>
       <c r="R7" t="n">
-        <v>6395395</v>
+        <v>6395372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,17 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosök, gran</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1330,17 +1337,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131475580</v>
+        <v>97646225</v>
       </c>
       <c r="B8" t="n">
-        <v>57911</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,42 +1355,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 61552, Försjönäs, Sm</t>
+          <t>Rumhult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575316</v>
+        <v>575261</v>
       </c>
       <c r="R8" t="n">
-        <v>6395394</v>
+        <v>6395111</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,17 +1409,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosök, gran</t>
+          <t>JMN0076 (Calluna AB) NVI.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,54 +1434,54 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131475653</v>
+        <v>130250050</v>
       </c>
       <c r="B9" t="n">
-        <v>92272</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1493,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575262</v>
       </c>
       <c r="R9" t="n">
-        <v>6395392</v>
+        <v>6395315</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,12 +1522,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,52 +1548,49 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131475471</v>
+        <v>130250024</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1602,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575295</v>
+        <v>575351</v>
       </c>
       <c r="R10" t="n">
-        <v>6395398</v>
+        <v>6395351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,12 +1628,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,7 +1647,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,52 +1658,49 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133532794</v>
+        <v>130250080</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575276</v>
+        <v>575236</v>
       </c>
       <c r="R11" t="n">
-        <v>6395404</v>
+        <v>6395421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,17 +1738,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På barklös granlåga!</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1757,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1772,21 +1768,21 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133532677</v>
+        <v>131475540</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1822,10 +1818,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575233</v>
+        <v>575309</v>
       </c>
       <c r="R12" t="n">
-        <v>6395408</v>
+        <v>6395395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,17 +1848,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bearbetat barkborregran</t>
+          <t>Födosök, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,17 +1878,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133532871</v>
+        <v>131475580</v>
       </c>
       <c r="B13" t="n">
-        <v>92356</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,34 +1896,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1935,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575311</v>
+        <v>575316</v>
       </c>
       <c r="R13" t="n">
-        <v>6395391</v>
+        <v>6395394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,17 +1958,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Lite osäker på substrat, men möjligen gran!</t>
+          <t>Födosök, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1984,7 +1977,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1996,21 +1988,21 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133533137</v>
+        <v>133532677</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2031,16 +2023,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2050,13 +2038,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575303</v>
+        <v>575233</v>
       </c>
       <c r="R14" t="n">
-        <v>6395378</v>
+        <v>6395408</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,6 +2074,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,6 +2102,548 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>97671771</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rumhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575271</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6395226</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>JSN0173 (Calluna AB) Fågelinventering.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldte spillning under flera tallar på bergshäll.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Frölinghaus</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133532474</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575246</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6395204</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133532514</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575253</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6395233</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133532970</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>575436</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6395187</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Drog iväg från högt träd</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130911242</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575307</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6395114</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61552-2025 artfynd.xlsx
+++ b/artfynd/A 61552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131475653</v>
+        <v>134599309</v>
       </c>
       <c r="B5" t="n">
-        <v>92333</v>
+        <v>92188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>3008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575305</v>
+        <v>575289</v>
       </c>
       <c r="R5" t="n">
-        <v>6395392</v>
+        <v>6395349</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133532871</v>
+        <v>131475653</v>
       </c>
       <c r="B6" t="n">
-        <v>92370</v>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575311</v>
+        <v>575305</v>
       </c>
       <c r="R6" t="n">
-        <v>6395391</v>
+        <v>6395392</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,17 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lite osäker på substrat, men möjligen gran!</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,63 +1223,63 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130250005</v>
+        <v>133532871</v>
       </c>
       <c r="B7" t="n">
-        <v>91867</v>
+        <v>92370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Försjönäs, Sm</t>
+          <t>A 61552, Försjönäs, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575585</v>
+        <v>575311</v>
       </c>
       <c r="R7" t="n">
-        <v>6395372</v>
+        <v>6395391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,12 +1306,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lite osäker på substrat, men möjligen gran!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97646225</v>
+        <v>130250005</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,34 +1355,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rumhult, Sm</t>
+          <t>Försjönäs, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575261</v>
+        <v>575585</v>
       </c>
       <c r="R8" t="n">
-        <v>6395111</v>
+        <v>6395372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,17 +1420,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>JMN0076 (Calluna AB) NVI.</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,25 +1434,26 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Österman</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130250050</v>
+        <v>97646225</v>
       </c>
       <c r="B9" t="n">
         <v>93235</v>
@@ -1474,28 +1481,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 61552, Försjönäs, Sm</t>
+          <t>Rumhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575262</v>
+        <v>575261</v>
       </c>
       <c r="R9" t="n">
-        <v>6395315</v>
+        <v>6395111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,12 +1518,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>JMN0076 (Calluna AB) NVI.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,61 +1537,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130250024</v>
+        <v>130250050</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1598,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575351</v>
+        <v>575262</v>
       </c>
       <c r="R10" t="n">
-        <v>6395351</v>
+        <v>6395315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,17 +1639,13 @@
           <t>2025-12-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1658,14 +1657,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130250080</v>
+        <v>130250024</v>
       </c>
       <c r="B11" t="n">
         <v>57950</v>
@@ -1708,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575236</v>
+        <v>575351</v>
       </c>
       <c r="R11" t="n">
-        <v>6395421</v>
+        <v>6395351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1747,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,14 +1767,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131475540</v>
+        <v>130250080</v>
       </c>
       <c r="B12" t="n">
         <v>57950</v>
@@ -1818,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575309</v>
+        <v>575236</v>
       </c>
       <c r="R12" t="n">
-        <v>6395395</v>
+        <v>6395421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,17 +1847,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosök, gran</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,14 +1877,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131475580</v>
+        <v>131475540</v>
       </c>
       <c r="B13" t="n">
         <v>57950</v>
@@ -1928,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575316</v>
+        <v>575309</v>
       </c>
       <c r="R13" t="n">
-        <v>6395394</v>
+        <v>6395395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133532677</v>
+        <v>131475580</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575233</v>
+        <v>575316</v>
       </c>
       <c r="R14" t="n">
-        <v>6395408</v>
+        <v>6395394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,17 +2067,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bearbetat barkborregran</t>
+          <t>Födosök, gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,17 +2097,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97671771</v>
+        <v>133532677</v>
       </c>
       <c r="B15" t="n">
-        <v>57141</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,39 +2115,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rumhult, Sm</t>
+          <t>A 61552, Försjönäs, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575271</v>
+        <v>575233</v>
       </c>
       <c r="R15" t="n">
-        <v>6395226</v>
+        <v>6395408</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,17 +2177,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-04-16</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>JSN0173 (Calluna AB) Fågelinventering.</t>
+          <t>Bearbetat barkborregran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,31 +2198,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>äldte spillning under flera tallar på bergshäll.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Frölinghaus</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133532474</v>
+        <v>134599041</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2225,21 +2225,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575246</v>
+        <v>575449</v>
       </c>
       <c r="R16" t="n">
-        <v>6395204</v>
+        <v>6395331</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,12 +2287,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,10 +2324,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133532514</v>
+        <v>134599235</v>
       </c>
       <c r="B17" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,21 +2335,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2352,7 +2357,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575253</v>
+        <v>575350</v>
       </c>
       <c r="R17" t="n">
-        <v>6395233</v>
+        <v>6395355</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,12 +2397,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2424,10 +2434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133532970</v>
+        <v>97671771</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,29 +2462,19 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 61552, Försjönäs, Sm</t>
+          <t>Rumhult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575436</v>
+        <v>575271</v>
       </c>
       <c r="R18" t="n">
-        <v>6395187</v>
+        <v>6395226</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Drog iväg från högt träd</t>
+          <t>JSN0173 (Calluna AB) Fågelinventering.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,60 +2522,61 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>äldte spillning under flera tallar på bergshäll.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Johan Frölinghaus</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130911242</v>
+        <v>133532474</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2585,13 +2586,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575307</v>
+        <v>575246</v>
       </c>
       <c r="R19" t="n">
-        <v>6395114</v>
+        <v>6395204</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2615,12 +2616,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,6 +2645,443 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133532514</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>575253</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6395233</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133532970</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>575436</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6395187</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Drog iväg från högt träd</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130911242</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>575307</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6395114</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134599000</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 61552, Försjönäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>575449</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6395331</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
